--- a/output/pdf_financials_xlsx/GUN.xlsx
+++ b/output/pdf_financials_xlsx/GUN.xlsx
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2.514903</v>
+        <v>-2.514903</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>27.528999</v>
@@ -1301,7 +1301,7 @@
         <v>-0.182</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>-9.87195</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -1521,16 +1521,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2.514903</v>
+        <v>-2.514903</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>17.858795</v>
+        <v>-17.858795</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>6.910472</v>
+        <v>-6.910472</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>4.935975</v>
+        <v>-4.935975</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-0.6432</v>
@@ -1686,16 +1686,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2.514903</v>
+        <v>-2.514903</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>17.858795</v>
+        <v>-17.858795</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.910472</v>
+        <v>-6.910472</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>4.935975</v>
+        <v>-4.935975</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-0.6432</v>
@@ -1855,16 +1855,16 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>5.46718</v>
+        <v>-5.46718</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>31.890705</v>
+        <v>-31.890705</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>36.370905</v>
+        <v>-36.370905</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>37.969038</v>
+        <v>-37.969038</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.514903</v>
+        <v>-2.514903</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>27.528999</v>
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2.514903</v>
+        <v>-2.514903</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>27.528999</v>
@@ -2174,7 +2174,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>35.12733608657547</v>
@@ -2183,7 +2183,7 @@
         <v>2.704923198015835</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -5621,46 +5621,46 @@
         <v>32.965031</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>41.357175</v>
+        <v>41.898153</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>41.399023</v>
+        <v>42.398689</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>41.509894</v>
+        <v>42.8231</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>43.0501</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>43.1501</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>43.6145</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>43.1446</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>43.2432</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>43.3165</v>
       </c>
       <c r="M92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>43.678</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>43.762</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>43.828</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>43.846</v>
       </c>
     </row>
     <row r="93">
@@ -9294,7 +9294,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10962,7 +10966,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -13406,7 +13414,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -17956,7 +17968,11 @@
           <t>Warrant reserve (note 15)</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -18050,7 +18066,11 @@
           <t>Share-based payments reserve (note 15)</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -22804,7 +22824,11 @@
           <t>Warrant reserve (note 14)</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -22900,7 +22924,11 @@
           <t>Share-based payments reserve (note 14)</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -72850,10 +72878,10 @@
         </is>
       </c>
       <c r="G682" s="5" t="n">
-        <v>6.910472</v>
+        <v>-6.910472</v>
       </c>
       <c r="H682" s="5" t="n">
-        <v>4.935975</v>
+        <v>-4.935975</v>
       </c>
       <c r="I682" t="inlineStr">
         <is>
@@ -76019,10 +76047,10 @@
         </is>
       </c>
       <c r="F715" s="5" t="n">
-        <v>17.858795</v>
+        <v>-17.858795</v>
       </c>
       <c r="G715" s="5" t="n">
-        <v>1.438703</v>
+        <v>-1.438703</v>
       </c>
       <c r="H715" t="inlineStr">
         <is>
@@ -78420,7 +78448,7 @@
         </is>
       </c>
       <c r="E740" s="5" t="n">
-        <v>2.514903</v>
+        <v>-2.514903</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GUN.xlsx
+++ b/output/pdf_financials_xlsx/GUN.xlsx
@@ -934,19 +934,19 @@
         <v>0.2289</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>0.547</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="11">
@@ -995,10 +995,10 @@
         <v>-0.2289</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0</v>
+        <v>-0.273</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>-0.547</v>
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000809</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000142</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-9.899999999999999e-05</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1925,13 +1925,13 @@
         <v>-2.514903</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>27.528999</v>
+        <v>27.529808</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>6.728472</v>
+        <v>6.728614</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>4.935975</v>
+        <v>4.936074</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.6432</v>
@@ -2035,13 +2035,13 @@
         <v>-2.514903</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>27.528999</v>
+        <v>27.529808</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>6.743269</v>
+        <v>6.743411</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>4.946922</v>
+        <v>4.947021</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.6377</v>
@@ -2326,10 +2326,10 @@
         <v>1.322163</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.241792</v>
+        <v>0.030396</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.107087</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1.552462</v>
@@ -2341,34 +2341,34 @@
         <v>0.0056</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.3652</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.1583</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.2796</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.0723</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.6535</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.145</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.328</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.788</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>3.807</v>
       </c>
     </row>
     <row r="35">
@@ -2436,10 +2436,10 @@
         <v>1.747146</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.241792</v>
+        <v>0.030396</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.3</v>
+        <v>0.407087</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>1.758712</v>
@@ -2451,34 +2451,34 @@
         <v>0.1072</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.3652</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.1583</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.2796</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.0723</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.6535</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.145</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.328</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.788</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>3.807</v>
       </c>
     </row>
     <row r="37">
@@ -3099,7 +3099,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.182482</v>
+        <v>0.075395</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -3111,34 +3111,34 @@
         <v>0.0091</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.3652</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.1845</v>
+        <v>0.0262</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.2906</v>
+        <v>0.011</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.0815</v>
+        <v>0.0092</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.66</v>
+        <v>0.0065</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.111</v>
+        <v>0.027</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.078</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.829</v>
+        <v>0.501</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.443</v>
+        <v>0.655</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>4.232</v>
+        <v>0.425</v>
       </c>
     </row>
     <row r="49">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -8724,7 +8724,11 @@
           <t>Reclamation deposits 8</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -9934,7 +9938,11 @@
           <t>Reclamation deposit 7</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -11350,7 +11358,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -12312,7 +12324,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -12682,7 +12694,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -14444,7 +14460,11 @@
           <t>Reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -16738,7 +16758,11 @@
           <t>Reclamation deposits (note 13)</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -21486,7 +21510,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -21872,7 +21896,11 @@
           <t>Reclamation deposits (note 12)</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -23304,7 +23332,11 @@
           <t>Reclamation deposits (note 11)</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -24454,7 +24486,11 @@
           <t>Reclamation deposit (note 10(b))</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E174" s="5" t="n">
         <v>0.002</v>
       </c>
@@ -42994,7 +43030,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -43090,7 +43130,11 @@
           <t>Refund of reclamation deposits</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
           <t>-</t>
@@ -45478,7 +45522,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
@@ -45572,7 +45620,11 @@
           <t>Refund of reclamation deposits</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
@@ -47010,7 +47062,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -53608,7 +53664,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -72184,7 +72240,7 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
@@ -75550,7 +75606,7 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
